--- a/Week_5/Heap_Sort/Heap Sort Chart.xlsx
+++ b/Week_5/Heap_Sort/Heap Sort Chart.xlsx
@@ -183,7 +183,7 @@
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
               </a:rPr>
-              <a:t>Merge Sort Complexity Analysis</a:t>
+              <a:t>Heap Sort Complexity Analysis</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -286,11 +286,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="1330651009"/>
-        <c:axId val="2120899748"/>
+        <c:axId val="1443407760"/>
+        <c:axId val="1291878330"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1330651009"/>
+        <c:axId val="1443407760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -346,10 +346,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2120899748"/>
+        <c:crossAx val="1291878330"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2120899748"/>
+        <c:axId val="1291878330"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -426,7 +426,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1330651009"/>
+        <c:crossAx val="1443407760"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
